--- a/241878_hw1_2025_1/ofertas_trabajo.xlsx
+++ b/241878_hw1_2025_1/ofertas_trabajo.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Publicado hace 6 días
+          <t>Publicado hace 7 días
 El Agustino, Lima, Peru
 IQFARMA, Laboratorio farmacéutico nacional con más de 61 años al servicio de la salud, dedicado a la fabricación y comercialización de productos de marca de diferentes especialidades farmacéuticas y genéricos de calidad que se distribuyen con gran éxito en el mercado privado e institucional. Actualmente nos encontramos en la búsqueda de: Analista de Tecnologías de la información.
 Descripción del puesto
@@ -513,7 +513,7 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Múltiples vacantes
-Actualizado hace 14 horas
+Actualizado ayer
 Pueblo Libre, Lima, Peru
 Descripción del puesto
 ZUTUN. es una empresa de software boutique con amplia experiencia en banca, seguros, fintech y retail. Nuestro colectivo funciona como un verdadero equipo, valorando la colaboración, la sinergia y el apoyo mutuo entre nuestros miembros, reconociendo que el talento es el núcleo y el equipo es quien juega el partido.
@@ -564,7 +564,7 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Múltiples vacantes
-Actualizado hace 15 horas
+Actualizado ayer
 Lima, Lima, Peru
 Descripción del puesto
 Importante empresa del sector, se encuentra en la búsqueda de un Analista Junior, Programador Power Builder que cumple con el siguiente perfil:
@@ -601,7 +601,7 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Múltiples vacantes
-Actualizado hace 13 horas
+Actualizado ayer
 Comas, Lima, Peru
 Descripción del puesto
 Summit Consulting es una empresa líder en soluciones tecnológicas, comprometida con el desarrollo de proyectos innovadores y la mejora constante de nuestros servicios. Actualmente, estamos en búsqueda de un Desarrollador Front-end Android altamente motivado y con experiencia para unirse a nuestro equipo dinámico.
@@ -668,7 +668,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Actualizado hace 13 horas
+          <t>Actualizado ayer
 Santa Anita, Lima, Peru
 Descripción del puesto
 Tecsup, instituto líder en educación tecnológica con 40 años en el mercado formando profesionales innovadores y éticos. Reconocido como una de las mejores instituciones educativas para trabajar. ¡Postula y únete a nuestra COMUNIDAD DE INNOVADORES!
@@ -717,7 +717,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Publicado hace 13 días
+          <t>Publicado hace 14 días
 Santiago de Surco, Lima, Peru
 Descripción del puesto
 Ven a Industrias San Miguel! ¡Somos un equipo unido por un mismo propósito! “Dar todo nuestro espíritu emprendedor para alimentar juntos un futuro próspero”. Intégrate como Desarrollador en Automatización en la sede Surco en Perú.
@@ -769,8 +769,7 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>Postulación rápida
-Nuevo
-Publicado hace 6 horas
+Publicado ayer
 San Isidro, Lima, Peru
 Descripción del puesto
 La Cámara de Comercio Exterior es una organización que tiene como propósito establecer lazos empresariales, los cuales incentivan, incrementan y desarrollan la economía a nivel internacional. A su vez, junto a su canal educativo, busca el crecimiento profesional de las personas gracias a nuestros cursos de educación continua.
@@ -806,8 +805,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nuevo
-Publicado hace 6 horas
+          <t>Publicado ayer
 San Isidro, Lima, Peru
 Descripción del puesto
 🚀 ¡Únete a Minsait como Desarrollador Full Stack Java + AngularJS Senior!
@@ -847,8 +845,7 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>Múltiples vacantes
-Nuevo
-Publicado hace 10 horas
+Publicado ayer
 Lima, Lima, Peru
 Descripción del puesto
 Entelgy Perú se estableció en 2014. En este breve periodo de tiempo ya ha conseguido, gracias a su experiencia internacional, grandes proyectos en distintos rubros, como en empresas de Distribución, Telecomunicaciones, Banca, Energía e Industria. Mantiene alianzas con organizaciones innovadoras y fabricantes líderes del sector con el fin de aportar más valor añadido y soluciones completas a las necesidades de sus clientes. Es partner de grandes fabricantes internacionales como SAP / OpenText, Liferay, Infovista, Qlikview, TTGuide.
@@ -899,8 +896,7 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>Múltiples vacantes
-Nuevo
-Publicado hace 12 horas
+Publicado ayer
 Cercado De Lima, Lima, Peru
 Descripción del puesto
 SOFTWARE ENTERPRISE SERVICES
@@ -945,8 +941,7 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>Postulación rápida
-Nuevo
-Publicado hace 14 horas
+Publicado ayer
 Jesús María, Lima, Peru
 Descripción del puesto
 La Universidad de San Martin de Porres te invita a participar en la selección de un analista programador :
@@ -1000,7 +995,7 @@
         <is>
           <t>Postulación rápida
 Múltiples vacantes
-Publicado hace 2 días
+Publicado hace 3 días
 Lima, Peru
 Descripción del puesto
 Actividades y Responsabilidades
@@ -1041,7 +1036,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Publicado hace 2 días
+          <t>Publicado hace 3 días
 San Isidro, Lima, Peru
 Descripción del puesto
 Somos una Empresa Transnacional especializada en Consultoría, tenemos más de 20 años de experiencia brindando soluciones especializadas pensadas de acuerdo a las necesidades de nuestros clientes. Contamos con una cartera de más de 1,500 clientes dentro de las operaciones de Grupo Siglo (Perú, Chile, Colombia, Ecuador, Panamá, Costa Rica y México). Somos líderes en brindar servicios de Consultoría contable, financiera y tributaria a importantes empresas de diferentes rubros a nivel nacional como internacional.
@@ -1084,7 +1079,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Actualizado hace 14 horas
+          <t>Actualizado ayer
 Lima, Lima, Peru
 Descripción del puesto
 CSTI Corp es una empresa peruana líder en la industria TI con más de 15 años en el mercado en países como Perú, Ecuador, Colombia, Costa Rica y Estados Unidos.
@@ -1119,7 +1114,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Actualizado hace 15 horas
+          <t>Actualizado ayer
 Lima, Lima, Peru
 Descripción del puesto
 CSTI Corp es una empresa peruana líder en la industria TI con más de 13 años en el mercado en países como Perú, Ecuador, Colombia, Costa Rica y Estados Unidos.
@@ -1152,7 +1147,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Actualizado hace 9 horas
+          <t>Actualizado ayer
 Lima, Lima, Peru
 Descripción del puesto
 CSTI Corp es una empresa peruana líder en la industria TI con más de 13 años en el mercado en países como Perú, Ecuador, Colombia, Costa Rica y Estados Unidos.
@@ -1186,7 +1181,7 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>Múltiples vacantes
-Actualizado hace 9 horas
+Actualizado ayer
 Lima, Lima, Peru
 Descripción del puesto
 Reinventa el futuro con Canvia!
@@ -1236,7 +1231,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Actualizado hace 12 horas
+          <t>Actualizado ayer
 Lima, Lima, Peru
 Descripción del puesto
 Somos una multinacional brasilera de soluciones digitales, con operación en diez países de América Latina. Apoyamos y evolucionamos los negocios de nuestros clientes a partir de nuestras cuatro líneas de negocios: Digital Business, Cloud Solutions, Digital Payments y Technology Platforms.
@@ -1278,7 +1273,7 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>Múltiples vacantes
-Publicado hace 3 días
+Publicado hace 4 días
 Lima, Lima, Peru
 Descripción del puesto
 Programador RPA
@@ -1328,7 +1323,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Actualizado hace 8 horas
+          <t>Actualizado ayer
 Miraflores, Lima, Peru
 Descripción del puesto
 Métrica Andina es la primera filial latinoamericana del grupo de consultoría español Métrica Consulting. El grupo comenzó operaciones con el inicio del nuevo siglo y desde entonces ha participado en distintos proyectos en distintos países de Europa Occidental y Latino América. Con Métrica Andina, hemos comenzado a ofrecer nuestros servicios técnicos en el mercado Peruano y desde ahí queremos llegar a la región andina en los próximos años.
